--- a/data/gravel/Mason Bokeh Ti 2025.xlsx
+++ b/data/gravel/Mason Bokeh Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA81E83-037E-8944-84FB-C440B725FE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5002ADBF-B36B-F947-AF7D-5B73AC268B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -275,9 +275,6 @@
     <t>Bokeh Ti</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>48CM</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>rear_axle_spec</t>
+  </si>
+  <si>
+    <t>GBP</t>
   </si>
 </sst>
 </file>
@@ -850,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -866,31 +866,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -903,10 +903,10 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="6">
         <v>480</v>
@@ -947,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="6">
         <v>433</v>
@@ -988,7 +988,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="6">
         <v>77</v>
@@ -1029,7 +1029,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="6">
         <v>435</v>
@@ -1070,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="6">
         <v>517</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="6">
         <v>500</v>
@@ -1152,7 +1152,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="6">
         <v>525</v>
@@ -1193,7 +1193,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" s="6">
         <v>364</v>
@@ -1234,7 +1234,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="6">
         <v>723</v>
@@ -1275,7 +1275,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="6">
         <v>50</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="6">
         <v>74.7</v>
@@ -1357,7 +1357,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="6">
         <v>398</v>
@@ -1398,7 +1398,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C21" s="6">
         <v>69.5</v>
@@ -1439,7 +1439,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="6">
         <v>100</v>
@@ -1480,7 +1480,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="6">
         <v>74</v>
@@ -1521,7 +1521,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="6">
         <v>1013</v>
@@ -1562,7 +1562,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" s="6">
         <v>40</v>
@@ -1603,7 +1603,7 @@
         <v>75</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="6">
         <v>590</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" s="6">
         <v>142</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="6">
         <v>515</v>
@@ -1740,7 +1740,7 @@
         <v>18</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C30" s="6">
         <v>70</v>
@@ -1781,7 +1781,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C31" s="6">
         <v>165</v>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C37">
         <v>151</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C38">
         <v>160</v>
@@ -2091,31 +2091,31 @@
         <v>68</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="E41" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="G41" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="I41" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="J41" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J41" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="K41" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -2399,7 +2399,7 @@
         <v>48</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -2674,7 +2674,7 @@
         <v>66</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>

--- a/data/gravel/Mason Bokeh Ti 2025.xlsx
+++ b/data/gravel/Mason Bokeh Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5002ADBF-B36B-F947-AF7D-5B73AC268B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475671CB-9368-9249-B6E4-1CB2DB5CDD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>GBP</t>
+  </si>
+  <si>
+    <t>https://masoncycles.cc/images/000/009/531/large/BokehTi2_GRX-Di2-2x_Side_Web.jpg?1744725585</t>
   </si>
 </sst>
 </file>
@@ -845,6 +848,11 @@
         <v>77</v>
       </c>
     </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+    </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Mason Bokeh Ti 2025.xlsx
+++ b/data/gravel/Mason Bokeh Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475671CB-9368-9249-B6E4-1CB2DB5CDD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D628C1D-63CA-B84F-BD48-53A512D84BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -426,6 +426,12 @@
   </si>
   <si>
     <t>https://masoncycles.cc/images/000/009/531/large/BokehTi2_GRX-Di2-2x_Side_Web.jpg?1744725585</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lancing, West Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -802,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S78"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2691,6 +2697,14 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" t="s">
+        <v>132</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/data/gravel/Mason Bokeh Ti 2025.xlsx
+++ b/data/gravel/Mason Bokeh Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D628C1D-63CA-B84F-BD48-53A512D84BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16129065-E9BA-6941-9A1E-8A19D794C8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -407,18 +407,9 @@
     <t>fork_weight</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>48/31</t>
   </si>
   <si>
-    <t>a8:j38</t>
-  </si>
-  <si>
     <t>rear_axle_spec</t>
   </si>
   <si>
@@ -432,6 +423,9 @@
   </si>
   <si>
     <t>Lancing, West Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>a8:j36</t>
   </si>
 </sst>
 </file>
@@ -808,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -856,7 +850,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -864,7 +858,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1655,7 +1649,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>106</v>
@@ -1941,37 +1935,29 @@
         <v>27</v>
       </c>
       <c r="B35" s="1"/>
-      <c r="C35" s="1">
-        <f>C37</f>
+      <c r="C35">
         <v>151</v>
       </c>
-      <c r="D35" s="1">
-        <f>AVERAGE(D37,C38)</f>
-        <v>158.5</v>
-      </c>
-      <c r="E35" s="1">
-        <f t="shared" ref="E35:I35" si="0">AVERAGE(E37,D38)</f>
-        <v>165.5</v>
-      </c>
-      <c r="F35" s="1">
-        <f t="shared" si="0"/>
-        <v>171</v>
-      </c>
-      <c r="G35" s="1">
-        <f t="shared" si="0"/>
-        <v>177.5</v>
-      </c>
-      <c r="H35" s="1">
-        <f t="shared" si="0"/>
-        <v>182.5</v>
-      </c>
-      <c r="I35" s="1">
-        <f t="shared" si="0"/>
-        <v>186.5</v>
-      </c>
-      <c r="J35" s="1">
-        <f>AVERAGE(J37,I38)</f>
-        <v>190.5</v>
+      <c r="D35">
+        <v>157</v>
+      </c>
+      <c r="E35">
+        <v>163</v>
+      </c>
+      <c r="F35">
+        <v>170</v>
+      </c>
+      <c r="G35">
+        <v>175</v>
+      </c>
+      <c r="H35">
+        <v>180</v>
+      </c>
+      <c r="I35">
+        <v>185</v>
+      </c>
+      <c r="J35" s="3">
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
@@ -1979,114 +1965,99 @@
         <v>28</v>
       </c>
       <c r="C36">
-        <f>D35</f>
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="D36">
-        <f t="shared" ref="D36:I36" si="1">E35</f>
-        <v>165.5</v>
+        <v>168</v>
       </c>
       <c r="E36">
-        <f t="shared" si="1"/>
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F36">
-        <f t="shared" si="1"/>
-        <v>177.5</v>
+        <v>180</v>
       </c>
       <c r="G36">
-        <f t="shared" si="1"/>
-        <v>182.5</v>
+        <v>185</v>
       </c>
       <c r="H36">
-        <f t="shared" si="1"/>
-        <v>186.5</v>
+        <v>188</v>
       </c>
       <c r="I36">
-        <f t="shared" si="1"/>
-        <v>190.5</v>
+        <v>193</v>
       </c>
       <c r="J36" s="1">
-        <f>J38</f>
         <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37">
-        <v>151</v>
-      </c>
-      <c r="D37">
-        <v>157</v>
-      </c>
-      <c r="E37">
-        <v>163</v>
-      </c>
-      <c r="F37">
-        <v>170</v>
-      </c>
-      <c r="G37">
-        <v>175</v>
-      </c>
-      <c r="H37">
-        <v>180</v>
-      </c>
-      <c r="I37">
-        <v>185</v>
-      </c>
-      <c r="J37" s="3">
-        <v>188</v>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38">
-        <v>160</v>
-      </c>
-      <c r="D38">
-        <v>168</v>
-      </c>
-      <c r="E38">
-        <v>172</v>
-      </c>
-      <c r="F38">
-        <v>180</v>
-      </c>
-      <c r="G38">
-        <v>185</v>
-      </c>
-      <c r="H38">
-        <v>188</v>
-      </c>
-      <c r="I38">
-        <v>193</v>
-      </c>
-      <c r="J38" s="1">
-        <v>198</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
+      <c r="A39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -2099,45 +2070,26 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>108</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -2150,27 +2102,25 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -2182,10 +2132,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>73</v>
+        <v>35</v>
+      </c>
+      <c r="B45" s="1">
+        <v>50</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -2198,9 +2148,11 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2.1</v>
+      </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -2212,11 +2164,9 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="1">
-        <v>50</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -2228,27 +2178,25 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="1">
-        <v>2.1</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2258,25 +2206,27 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="B51" s="1">
+        <v>142</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2286,9 +2236,11 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="B52" s="1">
+        <v>100</v>
+      </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -2300,10 +2252,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="1">
-        <v>142</v>
+        <v>43</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -2316,11 +2268,9 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="1">
-        <v>100</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -2332,10 +2282,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>76</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1">
+        <v>31.6</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -2348,9 +2298,11 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2362,10 +2314,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B57" s="1">
-        <v>31.6</v>
+        <v>42</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -2378,10 +2330,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -2394,10 +2346,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B59" s="1">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -2410,10 +2362,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>126</v>
+        <v>50</v>
+      </c>
+      <c r="B60" s="1">
+        <v>160</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -2426,11 +2378,9 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="1">
-        <v>160</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2442,10 +2392,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B62" s="1">
-        <v>160</v>
+        <v>52</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -2458,7 +2408,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2472,10 +2422,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -2488,7 +2438,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2502,10 +2452,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -2518,9 +2468,11 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2532,10 +2484,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" s="1">
-        <v>2</v>
+        <v>58</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2548,10 +2500,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -2560,11 +2512,10 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>73</v>
@@ -2576,11 +2527,10 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>73</v>
@@ -2595,7 +2545,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>73</v>
@@ -2610,10 +2560,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
+      </c>
+      <c r="B73" s="1">
+        <v>3800</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -2625,10 +2575,10 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
+      </c>
+      <c r="B74" s="1">
+        <v>5250</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -2640,10 +2590,10 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="1">
-        <v>3800</v>
+        <v>65</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -2655,10 +2605,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B76" s="1">
-        <v>5250</v>
+        <v>66</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -2669,41 +2619,11 @@
       <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="A77" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" t="s">
         <v>129</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Mason Bokeh Ti 2025.xlsx
+++ b/data/gravel/Mason Bokeh Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16129065-E9BA-6941-9A1E-8A19D794C8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4848942E-AFE4-AE4B-A367-5304B4AD9E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="137">
   <si>
     <t>brand</t>
   </si>
@@ -426,6 +426,24 @@
   </si>
   <si>
     <t>a8:j36</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -802,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2252,11 +2270,9 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -2268,7 +2284,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2282,11 +2298,9 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1">
-        <v>31.6</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -2298,11 +2312,9 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2314,11 +2326,9 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="1">
-        <v>42</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -2330,11 +2340,9 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -2346,10 +2354,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59" s="1">
-        <v>160</v>
+        <v>43</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -2362,11 +2370,9 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B60" s="1">
-        <v>160</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2378,9 +2384,11 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B61" s="1">
+        <v>31.6</v>
+      </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2392,10 +2400,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -2408,9 +2416,11 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="B63" s="1">
+        <v>42</v>
+      </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2422,10 +2432,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -2438,9 +2448,11 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B65" s="1">
+        <v>160</v>
+      </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2452,10 +2464,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B66" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -2468,11 +2480,9 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2484,10 +2494,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -2500,11 +2510,9 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2512,10 +2520,11 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>73</v>
@@ -2527,14 +2536,13 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2542,13 +2550,14 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2557,13 +2566,14 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B73" s="1">
-        <v>3800</v>
+        <v>1</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -2572,13 +2582,14 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="1">
-        <v>5250</v>
+        <v>58</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -2587,10 +2598,11 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>73</v>
@@ -2605,10 +2617,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -2619,10 +2631,100 @@
       <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="1">
+        <v>3800</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" s="1">
+        <v>5250</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>128</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B83" t="s">
         <v>129</v>
       </c>
     </row>
